--- a/lead_magnets/2026_外贸精准核价Excel模板.xlsx
+++ b/lead_magnets/2026_外贸精准核价Excel模板.xlsx
@@ -67,7 +67,7 @@
     <t>体验官网</t>
   </si>
   <si>
-    <t>https://quote.kelvinflow.com （联系创始人微信可免费协助跑测一份复杂询盘）</t>
+    <t>https://quote.kelvinflow.com （如需协助跑测复杂询盘，可在官方粉丝群内交流）</t>
   </si>
   <si>
     <t>产品SKU</t>
